--- a/.templates/FULL BOB TEMPLATE.xlsx
+++ b/.templates/FULL BOB TEMPLATE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rohini\Downloads\METlife-main\METlife-main\.templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsp-6\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{816C1D8F-6B13-4F8C-A6F9-FFBF3887C711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03CD5E96-E254-4A2E-AAFE-D8A576193EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D2B075CD-CE35-4D8D-BE2B-0B214D98E5CE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{87A946C8-B9D0-4F7D-B4C5-18FD6613F336}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,16 +34,392 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t xml:space="preserve">NOT COVERED </t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
+  <si>
+    <t xml:space="preserve"> Eligibility Verification - Full Form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Frequencies &amp; Limitations</t>
+  </si>
+  <si>
+    <t>Clinic Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         DIAGNOSTIC &amp; PREVENTIVE</t>
+  </si>
+  <si>
+    <t>Is the office in network?</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>Regular Oral Exams/ Does (D0120/D0150) share frequency ?</t>
+  </si>
+  <si>
+    <t>Appointment Date</t>
+  </si>
+  <si>
+    <t>Limted exams/ Does (D0140) share frequency with other exams?</t>
+  </si>
+  <si>
+    <t>Patient's Name, DOB</t>
+  </si>
+  <si>
+    <t>PA’s (D0220, D0230)</t>
+  </si>
+  <si>
+    <t>Subscriber's Name, DOB</t>
+  </si>
+  <si>
+    <t>Bitewings X-Ray (D0274)</t>
+  </si>
+  <si>
+    <t>Alternate/ Member ID#</t>
+  </si>
+  <si>
+    <t>Full Mouth X-Ray /Panoramic X-Ray (D0210 / D0330)</t>
+  </si>
+  <si>
+    <t>Insurace Name &amp; Tel#</t>
+  </si>
+  <si>
+    <t>Cone Beam (D0367)</t>
+  </si>
+  <si>
+    <t>Insurance claim mailing address:</t>
+  </si>
+  <si>
+    <t>Prophylaxis (D1110)</t>
+  </si>
+  <si>
+    <t>Claim filing limit</t>
+  </si>
+  <si>
+    <t>Fluoride (D1208)</t>
+  </si>
+  <si>
+    <t>Payer ID</t>
+  </si>
+  <si>
+    <t>Age limit for Fluoride?</t>
+  </si>
+  <si>
+    <t>Effective date</t>
+  </si>
+  <si>
+    <t>Sealants (D1351)</t>
+  </si>
+  <si>
+    <t>Plan renewal month?</t>
+  </si>
+  <si>
+    <t>Age limit for Sealants? Tooth Restrictions ?</t>
+  </si>
+  <si>
+    <t>Employer / Group name?</t>
+  </si>
+  <si>
+    <t>Group number?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        RESTORATIVE/ PERIO</t>
+  </si>
+  <si>
+    <t>Annual Maximum on the plan?</t>
+  </si>
+  <si>
+    <t>Posterior Composites/ Is (D2393) downgraded to Amalgam?</t>
+  </si>
+  <si>
+    <t>Remaining amount from the maximum ?</t>
+  </si>
+  <si>
+    <t>Crown/ Bridge (D2740/ D2750/ D6750)</t>
+  </si>
+  <si>
+    <t>Annual Individual Deductible?</t>
+  </si>
+  <si>
+    <t>Is D2740, D2750 or D6750 downgraded? If yes, which code? on molars or pre-molars?</t>
+  </si>
+  <si>
+    <t>Individual Deductible met?</t>
+  </si>
+  <si>
+    <t>Build up (D2950)</t>
+  </si>
+  <si>
+    <t>Annual Family Deductible?</t>
+  </si>
+  <si>
+    <t>Post &amp; Core (D2954)</t>
+  </si>
+  <si>
+    <t>Dependant age limit?</t>
+  </si>
+  <si>
+    <t>Recement Crown (D2920)</t>
+  </si>
+  <si>
+    <t>Fee schedule that the plan follows :</t>
+  </si>
+  <si>
+    <t>Crown Repair (D2980)</t>
+  </si>
+  <si>
+    <t>Coverage %</t>
+  </si>
+  <si>
+    <t>DED Applied? Yes/No</t>
+  </si>
+  <si>
+    <t>Percentage Coverage%</t>
+  </si>
+  <si>
+    <t>Diagnostic &amp; Preventive %</t>
+  </si>
+  <si>
+    <t>Crown Lengthening (D4249) Can crown be done on the same day?</t>
+  </si>
+  <si>
+    <t>Basic Restorative %</t>
+  </si>
+  <si>
+    <t>Scaling &amp; Root Planing (D4341/ D4342)</t>
+  </si>
+  <si>
+    <t>Endodontics %</t>
+  </si>
+  <si>
+    <t>Can 4 quadrants of SRP be done on the same day?</t>
+  </si>
+  <si>
+    <t>Periodontics %</t>
+  </si>
+  <si>
+    <t>Can Prophy(D1110) and SRP (D4341/D4342) be done on the same day?</t>
+  </si>
+  <si>
+    <t>Oral Surgery %</t>
+  </si>
+  <si>
+    <t>Gingival Scaling/ Does (D4346) share frequency with other cleaning? Any restriction?</t>
+  </si>
+  <si>
+    <t>Major Restorative %</t>
+  </si>
+  <si>
+    <t>Full Mouth Debridement (D4355)</t>
+  </si>
+  <si>
+    <t>Orthodontics %</t>
+  </si>
+  <si>
+    <t>Plan Provisions</t>
+  </si>
+  <si>
+    <t>Perio Maintenance (D4910)</t>
+  </si>
+  <si>
+    <t>Is there any Waiting Period? (If YES: Detail of WP)</t>
+  </si>
+  <si>
+    <t>Does Perio Maintenance (D4910) share frequency with prophy (D1110)?</t>
+  </si>
+  <si>
+    <t>Is there a Missing tooth clause?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                           IMPLANTS/ ORAL SURGERY/ ADJUNCTIVE</t>
+  </si>
+  <si>
+    <t>Are crowns paid on Prep or Seat date ?</t>
+  </si>
+  <si>
+    <t>Adjustment of Denture (D5410)</t>
+  </si>
+  <si>
+    <t>Crown Replacement Year/Month</t>
+  </si>
+  <si>
+    <t>Reline (D5740/ D5760)</t>
+  </si>
+  <si>
+    <t>Denture Replacement Year/Month</t>
+  </si>
+  <si>
+    <t>Implant (D6010)</t>
+  </si>
+  <si>
+    <t>Co-ordination of Benefits? Standard/Non duplication?</t>
+  </si>
+  <si>
+    <t>History</t>
+  </si>
+  <si>
+    <t>Exams</t>
+  </si>
+  <si>
+    <t>Recement (D6930)</t>
+  </si>
+  <si>
+    <t>Prophy</t>
+  </si>
+  <si>
+    <t>Simple Extraction (D7140)</t>
+  </si>
+  <si>
+    <t>Bitewings</t>
+  </si>
+  <si>
+    <t>Surgical Extraction (D7210)</t>
+  </si>
+  <si>
+    <t>FMX/Pano</t>
+  </si>
+  <si>
+    <t>Impacted soft tissue extraction (D7220)</t>
+  </si>
+  <si>
+    <t>Sealants</t>
+  </si>
+  <si>
+    <t>Do extractions need to go to medical insurance?</t>
+  </si>
+  <si>
+    <t>Fluoride</t>
+  </si>
+  <si>
+    <t>Bone Graft/ For (D7953) are extractions allowed on the same day?</t>
+  </si>
+  <si>
+    <t>Scaling &amp; Root Planing</t>
+  </si>
+  <si>
+    <t>Buccal/ Labial Frenectomy (D7961)</t>
+  </si>
+  <si>
+    <t>Additional Comments</t>
+  </si>
+  <si>
+    <t>Lingual Frenectomy (D7962)</t>
+  </si>
+  <si>
+    <t>Emergency Palliative/ For (D9110) are exams allowed on the same day?</t>
+  </si>
+  <si>
+    <t>Sedation (D9222, D9223)</t>
+  </si>
+  <si>
+    <t>Nitrous (D9230)</t>
+  </si>
+  <si>
+    <t>Consultation/ For (D9310) is same day treatment allowed?</t>
+  </si>
+  <si>
+    <t>Occlusal Guard/ Is (D9944) covered for Bruxism only?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         ORTHODONTICS</t>
+  </si>
+  <si>
+    <t>Ortho Lifetime Maximum?</t>
+  </si>
+  <si>
+    <t>Remaining Ortho maximum?</t>
+  </si>
+  <si>
+    <t>Ortho Deductibles? / Remaining ?</t>
+  </si>
+  <si>
+    <t>Ortho age limit?</t>
+  </si>
+  <si>
+    <t>Do you pay: Monthly / Quarterly / Annually?</t>
+  </si>
+  <si>
+    <t>Do we file: Once / Monthly / Quarterly?</t>
+  </si>
+  <si>
+    <t>Verification Date</t>
+  </si>
+  <si>
+    <t>Verified by</t>
+  </si>
+  <si>
+    <t>Insurance Representative Name</t>
+  </si>
+  <si>
+    <t>TUSK SUPPORT PARTNERS</t>
+  </si>
+  <si>
+    <t>Is work in progress a covered benefit?</t>
+  </si>
+  <si>
+    <t>Implant (D6058-D6059)</t>
+  </si>
+  <si>
+    <t>Implant (D6057)</t>
+  </si>
+  <si>
+    <t>Gingivectomy or Gingivoplasty (D4211)</t>
+  </si>
+  <si>
+    <t>Indirect Pulp Cap (D3120)</t>
+  </si>
+  <si>
+    <t>Pulpotomy (D3220)</t>
+  </si>
+  <si>
+    <t>Guided Tissue Regeneration (D4266) (Guidelines ?)</t>
+  </si>
+  <si>
+    <t>Covered if medically necessary?</t>
+  </si>
+  <si>
+    <t>What is the healing period between D4910 &amp; SRP?</t>
+  </si>
+  <si>
+    <t>Onlay - porcelain/ceramic (D2644)</t>
+  </si>
+  <si>
+    <t>Occlusal orthotic device, by report (D7880)</t>
+  </si>
+  <si>
+    <t>Pending claims / DOS ?</t>
+  </si>
+  <si>
+    <t>Gingivectomy (D4212) Can crown &amp; composite be done on the same day?</t>
+  </si>
+  <si>
+    <t>Interim caries arresting medicament application (D1354)</t>
+  </si>
+  <si>
+    <t>Caries Preventive Medicament Application (D1355)</t>
+  </si>
+  <si>
+    <t>Arestin (D4381)/Is it allowed on the same day with other periodontal services?
+Is it only covered after SRP is completed?If not what is the healing period?</t>
+  </si>
+  <si>
+    <t>Revised dt : 01.20.2026</t>
+  </si>
+  <si>
+    <t>Valley View Dental - Romeoville</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -51,16 +427,77 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6DFB3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="53">
     <border>
       <left/>
       <right/>
@@ -68,12 +505,1008 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -387,16 +1820,809 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6D5D694-676D-4015-8157-EF30C0251BFD}">
-  <dimension ref="E58"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{400E0B32-6A63-4920-A120-C91CE23E7CEB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="84.85546875" customWidth="1"/>
+    <col min="2" max="2" width="54.42578125" customWidth="1"/>
+    <col min="3" max="3" width="52.5703125" customWidth="1"/>
+    <col min="4" max="4" width="107.42578125" customWidth="1"/>
+    <col min="5" max="5" width="91.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="58" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E58" t="s">
+    <row r="1" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="99" t="s">
         <v>0</v>
       </c>
+      <c r="C1" s="100"/>
+      <c r="D1" s="101" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="102"/>
+    </row>
+    <row r="2" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="103" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="104"/>
+      <c r="D2" s="105" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="106"/>
+    </row>
+    <row r="3" spans="1:5" ht="21" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="107" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="108"/>
+      <c r="D3" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="24"/>
+    </row>
+    <row r="4" spans="1:5" ht="21" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="97"/>
+      <c r="C4" s="98"/>
+      <c r="D4" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="25"/>
+    </row>
+    <row r="5" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="83"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="25"/>
+    </row>
+    <row r="6" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="83"/>
+      <c r="C6" s="84"/>
+      <c r="D6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="25"/>
+    </row>
+    <row r="7" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="83"/>
+      <c r="C7" s="84"/>
+      <c r="D7" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="25"/>
+    </row>
+    <row r="8" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="83"/>
+      <c r="C8" s="84"/>
+      <c r="D8" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="25"/>
+    </row>
+    <row r="9" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="83"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="25"/>
+    </row>
+    <row r="10" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="88"/>
+      <c r="C10" s="89"/>
+      <c r="D10" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="25"/>
+    </row>
+    <row r="11" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="85"/>
+      <c r="C11" s="84"/>
+      <c r="D11" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="25"/>
+    </row>
+    <row r="12" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="109"/>
+      <c r="C12" s="110"/>
+      <c r="D12" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="25"/>
+    </row>
+    <row r="13" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="83"/>
+      <c r="C13" s="84"/>
+      <c r="D13" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="25"/>
+    </row>
+    <row r="14" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="83"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" s="45"/>
+    </row>
+    <row r="15" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="85"/>
+      <c r="C15" s="84"/>
+      <c r="D15" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="E15" s="33"/>
+    </row>
+    <row r="16" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="86"/>
+      <c r="C16" s="87"/>
+      <c r="D16" s="101" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="102"/>
+    </row>
+    <row r="17" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="86"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="34"/>
+    </row>
+    <row r="18" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="86"/>
+      <c r="C18" s="87"/>
+      <c r="D18" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="E18" s="25"/>
+    </row>
+    <row r="19" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="86"/>
+      <c r="C19" s="87"/>
+      <c r="D19" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="33"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="32"/>
+    </row>
+    <row r="20" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="86"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="35"/>
+    </row>
+    <row r="21" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="88"/>
+      <c r="C21" s="89"/>
+      <c r="D21" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="34"/>
+    </row>
+    <row r="22" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="90"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="34"/>
+    </row>
+    <row r="23" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="25"/>
+    </row>
+    <row r="24" spans="1:7" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A24" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="26"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="25"/>
+    </row>
+    <row r="25" spans="1:7" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A25" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="27"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" s="25"/>
+    </row>
+    <row r="26" spans="1:7" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A26" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="27"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E26" s="25"/>
+    </row>
+    <row r="27" spans="1:7" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A27" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="27"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27" s="25"/>
+    </row>
+    <row r="28" spans="1:7" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A28" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="27"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E28" s="25"/>
+    </row>
+    <row r="29" spans="1:7" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A29" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="27"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29" s="25"/>
+    </row>
+    <row r="30" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="28"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="E30" s="25"/>
+    </row>
+    <row r="31" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="66" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="92"/>
+      <c r="C31" s="92"/>
+      <c r="D31" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E31" s="25"/>
+    </row>
+    <row r="32" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A32" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="93"/>
+      <c r="C32" s="94"/>
+      <c r="D32" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E32" s="25"/>
+    </row>
+    <row r="33" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A33" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="68"/>
+      <c r="C33" s="69"/>
+      <c r="D33" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E33" s="25"/>
+    </row>
+    <row r="34" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A34" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="68"/>
+      <c r="C34" s="69"/>
+      <c r="D34" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E34" s="25"/>
+    </row>
+    <row r="35" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="68"/>
+      <c r="C35" s="69"/>
+      <c r="D35" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E35" s="25"/>
+    </row>
+    <row r="36" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="68"/>
+      <c r="C36" s="69"/>
+      <c r="D36" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E36" s="25"/>
+    </row>
+    <row r="37" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" s="79"/>
+      <c r="C37" s="80"/>
+      <c r="D37" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E37" s="25"/>
+    </row>
+    <row r="38" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="81" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" s="82"/>
+      <c r="C38" s="82"/>
+      <c r="D38" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E38" s="25"/>
+    </row>
+    <row r="39" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" s="70"/>
+      <c r="C39" s="71"/>
+      <c r="D39" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="E39" s="31"/>
+    </row>
+    <row r="40" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" s="70"/>
+      <c r="C40" s="71"/>
+      <c r="D40" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="E40" s="67"/>
+    </row>
+    <row r="41" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="70"/>
+      <c r="C41" s="71"/>
+      <c r="D41" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E41" s="49"/>
+    </row>
+    <row r="42" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" s="72"/>
+      <c r="C42" s="71"/>
+      <c r="D42" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="50"/>
+    </row>
+    <row r="43" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="72"/>
+      <c r="C43" s="71"/>
+      <c r="D43" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E43" s="50"/>
+    </row>
+    <row r="44" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" s="72"/>
+      <c r="C44" s="71"/>
+      <c r="D44" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E44" s="50"/>
+    </row>
+    <row r="45" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B45" s="72"/>
+      <c r="C45" s="71"/>
+      <c r="D45" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="E45" s="50"/>
+    </row>
+    <row r="46" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A46" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="B46" s="75"/>
+      <c r="C46" s="76"/>
+      <c r="D46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E46" s="50"/>
+    </row>
+    <row r="47" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A47" s="73"/>
+      <c r="B47" s="77"/>
+      <c r="C47" s="77"/>
+      <c r="D47" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E47" s="52"/>
+    </row>
+    <row r="48" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A48" s="73"/>
+      <c r="B48" s="77"/>
+      <c r="C48" s="77"/>
+      <c r="D48" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E48" s="53"/>
+    </row>
+    <row r="49" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A49" s="73"/>
+      <c r="B49" s="77"/>
+      <c r="C49" s="77"/>
+      <c r="D49" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E49" s="53"/>
+    </row>
+    <row r="50" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="74"/>
+      <c r="B50" s="78"/>
+      <c r="C50" s="78"/>
+      <c r="D50" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E50" s="50"/>
+    </row>
+    <row r="51" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A51" s="57" t="s">
+        <v>117</v>
+      </c>
+      <c r="B51" s="60"/>
+      <c r="C51" s="61"/>
+      <c r="D51" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E51" s="50"/>
+    </row>
+    <row r="52" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A52" s="58"/>
+      <c r="B52" s="62"/>
+      <c r="C52" s="63"/>
+      <c r="D52" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E52" s="50"/>
+    </row>
+    <row r="53" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A53" s="58"/>
+      <c r="B53" s="62"/>
+      <c r="C53" s="63"/>
+      <c r="D53" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E53" s="50"/>
+    </row>
+    <row r="54" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A54" s="58"/>
+      <c r="B54" s="62"/>
+      <c r="C54" s="63"/>
+      <c r="D54" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="E54" s="50"/>
+    </row>
+    <row r="55" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="59"/>
+      <c r="B55" s="64"/>
+      <c r="C55" s="65"/>
+      <c r="D55" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E55" s="50"/>
+    </row>
+    <row r="56" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="95" t="s">
+        <v>122</v>
+      </c>
+      <c r="B56" s="96"/>
+      <c r="C56" s="96"/>
+      <c r="D56" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="E56" s="50"/>
+    </row>
+    <row r="57" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A57" s="11"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="E57" s="50"/>
+    </row>
+    <row r="58" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A58" s="11"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E58" s="50"/>
+    </row>
+    <row r="59" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="11"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="E59" s="51"/>
+    </row>
+    <row r="60" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="E60" s="67"/>
+    </row>
+    <row r="61" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A61" s="11"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="E61" s="54"/>
+    </row>
+    <row r="62" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A62" s="11"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="E62" s="55" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A63" s="11"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="11"/>
+      <c r="D63" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E63" s="56"/>
+    </row>
+    <row r="64" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A64" s="11"/>
+      <c r="B64" s="11"/>
+      <c r="C64" s="11"/>
+      <c r="D64" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="E64" s="29"/>
+    </row>
+    <row r="65" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A65" s="11"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E65" s="29"/>
+    </row>
+    <row r="66" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A66" s="11"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E66" s="29"/>
+    </row>
+    <row r="67" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A67" s="11"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E67" s="29"/>
+    </row>
+    <row r="68" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D68" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="E68" s="30"/>
+    </row>
+    <row r="69" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D69" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="E69" s="42"/>
+    </row>
+    <row r="70" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D70" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E70" s="43"/>
+    </row>
+    <row r="71" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D71" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="E71" s="44"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <mergeCells count="47">
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A51:A55"/>
+    <mergeCell ref="B51:C55"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="A46:A50"/>
+    <mergeCell ref="B46:C50"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="B39:C39"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.46" right="0.35" top="0.44" bottom="0.1" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="8" scale="53" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/.templates/FULL BOB TEMPLATE.xlsx
+++ b/.templates/FULL BOB TEMPLATE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsp-6\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsp-6\Downloads\Metlife-main-main (1)\Metlife-main-main\.templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03CD5E96-E254-4A2E-AAFE-D8A576193EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63458549-9488-4830-A697-B03E81AFB6C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{87A946C8-B9D0-4F7D-B4C5-18FD6613F336}"/>
   </bookViews>
@@ -1345,38 +1345,101 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1384,14 +1447,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1422,90 +1506,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1838,36 +1838,36 @@
       <c r="A1" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="99" t="s">
+      <c r="B1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="100"/>
-      <c r="D1" s="101" t="s">
+      <c r="C1" s="62"/>
+      <c r="D1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="102"/>
+      <c r="E1" s="64"/>
     </row>
     <row r="2" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="103" t="s">
+      <c r="B2" s="65" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="104"/>
-      <c r="D2" s="105" t="s">
+      <c r="C2" s="66"/>
+      <c r="D2" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="106"/>
+      <c r="E2" s="68"/>
     </row>
     <row r="3" spans="1:5" ht="21" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="108"/>
+      <c r="C3" s="70"/>
       <c r="D3" s="22" t="s">
         <v>6</v>
       </c>
@@ -1877,8 +1877,8 @@
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="97"/>
-      <c r="C4" s="98"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="60"/>
       <c r="D4" s="15" t="s">
         <v>8</v>
       </c>
@@ -1888,8 +1888,8 @@
       <c r="A5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="83"/>
-      <c r="C5" s="84"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="72"/>
       <c r="D5" s="14" t="s">
         <v>10</v>
       </c>
@@ -1899,8 +1899,8 @@
       <c r="A6" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="83"/>
-      <c r="C6" s="84"/>
+      <c r="B6" s="71"/>
+      <c r="C6" s="72"/>
       <c r="D6" s="14" t="s">
         <v>12</v>
       </c>
@@ -1910,8 +1910,8 @@
       <c r="A7" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="84"/>
+      <c r="B7" s="71"/>
+      <c r="C7" s="72"/>
       <c r="D7" s="14" t="s">
         <v>14</v>
       </c>
@@ -1921,8 +1921,8 @@
       <c r="A8" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="83"/>
-      <c r="C8" s="84"/>
+      <c r="B8" s="71"/>
+      <c r="C8" s="72"/>
       <c r="D8" s="14" t="s">
         <v>16</v>
       </c>
@@ -1932,8 +1932,8 @@
       <c r="A9" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="83"/>
-      <c r="C9" s="84"/>
+      <c r="B9" s="71"/>
+      <c r="C9" s="72"/>
       <c r="D9" s="14" t="s">
         <v>18</v>
       </c>
@@ -1943,8 +1943,8 @@
       <c r="A10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="88"/>
-      <c r="C10" s="89"/>
+      <c r="B10" s="73"/>
+      <c r="C10" s="74"/>
       <c r="D10" s="14" t="s">
         <v>20</v>
       </c>
@@ -1954,8 +1954,8 @@
       <c r="A11" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="85"/>
-      <c r="C11" s="84"/>
+      <c r="B11" s="75"/>
+      <c r="C11" s="72"/>
       <c r="D11" s="15" t="s">
         <v>22</v>
       </c>
@@ -1965,8 +1965,8 @@
       <c r="A12" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="109"/>
-      <c r="C12" s="110"/>
+      <c r="B12" s="76"/>
+      <c r="C12" s="77"/>
       <c r="D12" s="14" t="s">
         <v>24</v>
       </c>
@@ -1976,8 +1976,8 @@
       <c r="A13" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="83"/>
-      <c r="C13" s="84"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="72"/>
       <c r="D13" s="14" t="s">
         <v>26</v>
       </c>
@@ -1987,8 +1987,8 @@
       <c r="A14" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="83"/>
-      <c r="C14" s="84"/>
+      <c r="B14" s="71"/>
+      <c r="C14" s="72"/>
       <c r="D14" s="3" t="s">
         <v>119</v>
       </c>
@@ -1998,8 +1998,8 @@
       <c r="A15" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="85"/>
-      <c r="C15" s="84"/>
+      <c r="B15" s="75"/>
+      <c r="C15" s="72"/>
       <c r="D15" s="47" t="s">
         <v>120</v>
       </c>
@@ -2009,19 +2009,19 @@
       <c r="A16" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="86"/>
-      <c r="C16" s="87"/>
-      <c r="D16" s="101" t="s">
+      <c r="B16" s="81"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="102"/>
+      <c r="E16" s="64"/>
     </row>
     <row r="17" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="86"/>
-      <c r="C17" s="87"/>
+      <c r="B17" s="81"/>
+      <c r="C17" s="82"/>
       <c r="D17" s="46" t="s">
         <v>31</v>
       </c>
@@ -2031,8 +2031,8 @@
       <c r="A18" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="86"/>
-      <c r="C18" s="87"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="82"/>
       <c r="D18" s="14" t="s">
         <v>115</v>
       </c>
@@ -2042,8 +2042,8 @@
       <c r="A19" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="86"/>
-      <c r="C19" s="87"/>
+      <c r="B19" s="81"/>
+      <c r="C19" s="82"/>
       <c r="D19" s="15" t="s">
         <v>33</v>
       </c>
@@ -2055,8 +2055,8 @@
       <c r="A20" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="86"/>
-      <c r="C20" s="87"/>
+      <c r="B20" s="81"/>
+      <c r="C20" s="82"/>
       <c r="D20" s="5" t="s">
         <v>35</v>
       </c>
@@ -2066,8 +2066,8 @@
       <c r="A21" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="88"/>
-      <c r="C21" s="89"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="74"/>
       <c r="D21" s="14" t="s">
         <v>37</v>
       </c>
@@ -2077,8 +2077,8 @@
       <c r="A22" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="90"/>
-      <c r="C22" s="91"/>
+      <c r="B22" s="83"/>
+      <c r="C22" s="84"/>
       <c r="D22" s="14" t="s">
         <v>39</v>
       </c>
@@ -2177,11 +2177,11 @@
       <c r="E30" s="25"/>
     </row>
     <row r="31" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="66" t="s">
+      <c r="A31" s="85" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="92"/>
-      <c r="C31" s="92"/>
+      <c r="B31" s="86"/>
+      <c r="C31" s="86"/>
       <c r="D31" s="14" t="s">
         <v>50</v>
       </c>
@@ -2191,8 +2191,8 @@
       <c r="A32" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="93"/>
-      <c r="C32" s="94"/>
+      <c r="B32" s="87"/>
+      <c r="C32" s="88"/>
       <c r="D32" s="9" t="s">
         <v>52</v>
       </c>
@@ -2202,8 +2202,8 @@
       <c r="A33" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="68"/>
-      <c r="C33" s="69"/>
+      <c r="B33" s="89"/>
+      <c r="C33" s="90"/>
       <c r="D33" s="9" t="s">
         <v>54</v>
       </c>
@@ -2213,8 +2213,8 @@
       <c r="A34" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B34" s="68"/>
-      <c r="C34" s="69"/>
+      <c r="B34" s="89"/>
+      <c r="C34" s="90"/>
       <c r="D34" s="9" t="s">
         <v>56</v>
       </c>
@@ -2224,8 +2224,8 @@
       <c r="A35" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="B35" s="68"/>
-      <c r="C35" s="69"/>
+      <c r="B35" s="89"/>
+      <c r="C35" s="90"/>
       <c r="D35" s="14" t="s">
         <v>58</v>
       </c>
@@ -2235,8 +2235,8 @@
       <c r="A36" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="68"/>
-      <c r="C36" s="69"/>
+      <c r="B36" s="89"/>
+      <c r="C36" s="90"/>
       <c r="D36" s="40" t="s">
         <v>121</v>
       </c>
@@ -2246,19 +2246,19 @@
       <c r="A37" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="79"/>
-      <c r="C37" s="80"/>
+      <c r="B37" s="107"/>
+      <c r="C37" s="108"/>
       <c r="D37" s="14" t="s">
         <v>61</v>
       </c>
       <c r="E37" s="25"/>
     </row>
     <row r="38" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="81" t="s">
+      <c r="A38" s="109" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="82"/>
-      <c r="C38" s="82"/>
+      <c r="B38" s="110"/>
+      <c r="C38" s="110"/>
       <c r="D38" s="9" t="s">
         <v>114</v>
       </c>
@@ -2268,8 +2268,8 @@
       <c r="A39" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="70"/>
-      <c r="C39" s="71"/>
+      <c r="B39" s="78"/>
+      <c r="C39" s="79"/>
       <c r="D39" s="41" t="s">
         <v>63</v>
       </c>
@@ -2279,19 +2279,19 @@
       <c r="A40" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B40" s="70"/>
-      <c r="C40" s="71"/>
-      <c r="D40" s="66" t="s">
+      <c r="B40" s="78"/>
+      <c r="C40" s="79"/>
+      <c r="D40" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="E40" s="67"/>
+      <c r="E40" s="100"/>
     </row>
     <row r="41" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B41" s="70"/>
-      <c r="C41" s="71"/>
+      <c r="B41" s="78"/>
+      <c r="C41" s="79"/>
       <c r="D41" s="17" t="s">
         <v>67</v>
       </c>
@@ -2301,8 +2301,8 @@
       <c r="A42" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="72"/>
-      <c r="C42" s="71"/>
+      <c r="B42" s="80"/>
+      <c r="C42" s="79"/>
       <c r="D42" s="14" t="s">
         <v>69</v>
       </c>
@@ -2312,8 +2312,8 @@
       <c r="A43" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B43" s="72"/>
-      <c r="C43" s="71"/>
+      <c r="B43" s="80"/>
+      <c r="C43" s="79"/>
       <c r="D43" s="14" t="s">
         <v>71</v>
       </c>
@@ -2323,8 +2323,8 @@
       <c r="A44" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B44" s="72"/>
-      <c r="C44" s="71"/>
+      <c r="B44" s="80"/>
+      <c r="C44" s="79"/>
       <c r="D44" s="14" t="s">
         <v>108</v>
       </c>
@@ -2334,113 +2334,113 @@
       <c r="A45" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B45" s="72"/>
-      <c r="C45" s="71"/>
+      <c r="B45" s="80"/>
+      <c r="C45" s="79"/>
       <c r="D45" s="14" t="s">
         <v>107</v>
       </c>
       <c r="E45" s="50"/>
     </row>
     <row r="46" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A46" s="57" t="s">
+      <c r="A46" s="91" t="s">
         <v>88</v>
       </c>
-      <c r="B46" s="75"/>
-      <c r="C46" s="76"/>
+      <c r="B46" s="103"/>
+      <c r="C46" s="104"/>
       <c r="D46" s="14" t="s">
         <v>75</v>
       </c>
       <c r="E46" s="50"/>
     </row>
     <row r="47" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A47" s="73"/>
-      <c r="B47" s="77"/>
-      <c r="C47" s="77"/>
+      <c r="A47" s="101"/>
+      <c r="B47" s="105"/>
+      <c r="C47" s="105"/>
       <c r="D47" s="14" t="s">
         <v>77</v>
       </c>
       <c r="E47" s="52"/>
     </row>
     <row r="48" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A48" s="73"/>
-      <c r="B48" s="77"/>
-      <c r="C48" s="77"/>
+      <c r="A48" s="101"/>
+      <c r="B48" s="105"/>
+      <c r="C48" s="105"/>
       <c r="D48" s="14" t="s">
         <v>79</v>
       </c>
       <c r="E48" s="53"/>
     </row>
     <row r="49" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A49" s="73"/>
-      <c r="B49" s="77"/>
-      <c r="C49" s="77"/>
+      <c r="A49" s="101"/>
+      <c r="B49" s="105"/>
+      <c r="C49" s="105"/>
       <c r="D49" s="14" t="s">
         <v>81</v>
       </c>
       <c r="E49" s="53"/>
     </row>
     <row r="50" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="74"/>
-      <c r="B50" s="78"/>
-      <c r="C50" s="78"/>
+      <c r="A50" s="102"/>
+      <c r="B50" s="106"/>
+      <c r="C50" s="106"/>
       <c r="D50" s="9" t="s">
         <v>83</v>
       </c>
       <c r="E50" s="50"/>
     </row>
     <row r="51" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A51" s="57" t="s">
+      <c r="A51" s="91" t="s">
         <v>117</v>
       </c>
-      <c r="B51" s="60"/>
-      <c r="C51" s="61"/>
+      <c r="B51" s="94"/>
+      <c r="C51" s="95"/>
       <c r="D51" s="9" t="s">
         <v>116</v>
       </c>
       <c r="E51" s="50"/>
     </row>
     <row r="52" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A52" s="58"/>
-      <c r="B52" s="62"/>
-      <c r="C52" s="63"/>
+      <c r="A52" s="92"/>
+      <c r="B52" s="96"/>
+      <c r="C52" s="97"/>
       <c r="D52" s="9" t="s">
         <v>85</v>
       </c>
       <c r="E52" s="50"/>
     </row>
     <row r="53" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A53" s="58"/>
-      <c r="B53" s="62"/>
-      <c r="C53" s="63"/>
+      <c r="A53" s="92"/>
+      <c r="B53" s="96"/>
+      <c r="C53" s="97"/>
       <c r="D53" s="14" t="s">
         <v>87</v>
       </c>
       <c r="E53" s="50"/>
     </row>
     <row r="54" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A54" s="58"/>
-      <c r="B54" s="62"/>
-      <c r="C54" s="63"/>
+      <c r="A54" s="92"/>
+      <c r="B54" s="96"/>
+      <c r="C54" s="97"/>
       <c r="D54" s="14" t="s">
         <v>89</v>
       </c>
       <c r="E54" s="50"/>
     </row>
     <row r="55" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="59"/>
-      <c r="B55" s="64"/>
-      <c r="C55" s="65"/>
+      <c r="A55" s="93"/>
+      <c r="B55" s="98"/>
+      <c r="C55" s="99"/>
       <c r="D55" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E55" s="50"/>
     </row>
     <row r="56" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="95" t="s">
+      <c r="A56" s="57" t="s">
         <v>122</v>
       </c>
-      <c r="B56" s="96"/>
-      <c r="C56" s="96"/>
+      <c r="B56" s="58"/>
+      <c r="C56" s="58"/>
       <c r="D56" s="14" t="s">
         <v>91</v>
       </c>
@@ -2477,10 +2477,10 @@
       <c r="A60" s="11"/>
       <c r="B60" s="12"/>
       <c r="C60" s="11"/>
-      <c r="D60" s="66" t="s">
+      <c r="D60" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="E60" s="67"/>
+      <c r="E60" s="100"/>
     </row>
     <row r="61" spans="1:5" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A61" s="11"/>
@@ -2573,6 +2573,37 @@
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="A51:A55"/>
+    <mergeCell ref="B51:C55"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="A46:A50"/>
+    <mergeCell ref="B46:C50"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="A56:C56"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B1:C1"/>
@@ -2589,37 +2620,6 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A51:A55"/>
-    <mergeCell ref="B51:C55"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="A46:A50"/>
-    <mergeCell ref="B46:C50"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="B39:C39"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.46" right="0.35" top="0.44" bottom="0.1" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/.templates/FULL BOB TEMPLATE.xlsx
+++ b/.templates/FULL BOB TEMPLATE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsp-6\Downloads\Metlife-main-main (1)\Metlife-main-main\.templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsp-6\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63458549-9488-4830-A697-B03E81AFB6C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03CD5E96-E254-4A2E-AAFE-D8A576193EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{87A946C8-B9D0-4F7D-B4C5-18FD6613F336}"/>
   </bookViews>
